--- a/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1178,6 +1178,16 @@
           <t>BatchRecipeId</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ManualRecipeId</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>BakeRecipeId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1215,6 +1225,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1252,6 +1272,16 @@
           <t>BatchRecipeId</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ManualRecipeId</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BakeRecipeId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1289,6 +1319,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1326,6 +1366,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1359,6 +1409,110 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>利落切配</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>均匀烘焙</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>StationWorkKind</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Chop</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1489,14 +1489,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>4</t>
@@ -1516,6 +1516,461 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>利落切橙</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>轻快切菜</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>清脆切配</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>高效果汁</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>均匀煎肉</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>香肠快煎</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>从容煎蛋</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>顺滑搅拌</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>蓬松烘焙</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>细致研磨</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>稳定萃取</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>暖心热奶</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>绵密奶泡</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/BuffConfig.xlsx
@@ -1,319 +1,203 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnitProto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int&amp;group=c</t>
-  </si>
-  <si>
-    <t>int&amp;group=s</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>测试说明</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>位置</t>
-  </si>
-  <si>
-    <t>身高</t>
-  </si>
-  <si>
-    <t>体重</t>
-  </si>
-  <si>
-    <t>米克尔</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能</t>
-  </si>
-  <si>
-    <t>测试说明2</t>
-  </si>
-  <si>
-    <t>米克尔2</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能2</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>米克尔3</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能3</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>米克尔4</t>
-  </si>
-  <si>
-    <t>带有强力攻击技能4</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="24">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -620,163 +504,163 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -833,11 +717,74 @@
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1127,19 +1074,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr/>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col width="21.125" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.75" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="15.125" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="28.75" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11.75" customWidth="1" style="2" min="8" max="9"/>
+    <col width="6.75" customWidth="1" style="2" min="10" max="10"/>
+    <col width="9" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1284,11 +1234,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>1</t>
@@ -1331,11 +1276,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2</t>
@@ -1378,11 +1318,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>3</t>
@@ -1425,11 +1360,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1472,11 +1402,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1519,12 +1444,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1537,29 +1457,24 @@
           <t>Chop</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1572,29 +1487,24 @@
           <t>Chop</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>8</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1607,29 +1517,24 @@
           <t>Chop</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1642,29 +1547,24 @@
           <t>Batch</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1677,29 +1577,24 @@
           <t>Bake</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1712,29 +1607,24 @@
           <t>Bake</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1747,29 +1637,24 @@
           <t>Bake</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>13</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1782,29 +1667,24 @@
           <t>Batch</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1817,29 +1697,24 @@
           <t>Bake</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>15</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1852,29 +1727,24 @@
           <t>Bake</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>4</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>16</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1887,29 +1757,24 @@
           <t>Batch</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>4</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>17</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1922,29 +1787,24 @@
           <t>Batch</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>18</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1957,25 +1817,144 @@
           <t>Batch</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>4</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>6</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>轻快切葱</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Chop</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>均匀蒸制</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>专注泡茶</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>顺手调饮</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>